--- a/diag/mfg/scripts/logserver/Penang_Chamber_Config.xlsx
+++ b/diag/mfg/scripts/logserver/Penang_Chamber_Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charles Fung\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srv1\home\winson\worksapce\psdiag\diag\mfg\scripts\logserver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57A8576D-D25A-4721-8757-487E1B3EDB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B7D5E1-A836-42D0-9AD7-E727E2574EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{5B8EDC0A-7C03-4D41-A1A0-33B6A1F1AC78}"/>
+    <workbookView xWindow="866" yWindow="-103" windowWidth="27008" windowHeight="18720" xr2:uid="{5B8EDC0A-7C03-4D41-A1A0-33B6A1F1AC78}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="80">
   <si>
     <t>Chamber 1</t>
   </si>
@@ -75,9 +75,6 @@
     <t>MTP-634</t>
   </si>
   <si>
-    <t>MTP-744</t>
-  </si>
-  <si>
     <t>MTP-615</t>
   </si>
   <si>
@@ -186,9 +183,6 @@
     <t>MTP-750</t>
   </si>
   <si>
-    <t>MTP-644</t>
-  </si>
-  <si>
     <t>MTP-712</t>
   </si>
   <si>
@@ -247,13 +241,46 @@
   </si>
   <si>
     <t>MTP-751</t>
+  </si>
+  <si>
+    <t>FLOOR</t>
+  </si>
+  <si>
+    <t>FLOOR_8</t>
+  </si>
+  <si>
+    <t>FLOOR_7</t>
+  </si>
+  <si>
+    <t>FLOOR_6</t>
+  </si>
+  <si>
+    <t>FLOOR_5</t>
+  </si>
+  <si>
+    <t>FLOOR_4</t>
+  </si>
+  <si>
+    <t>FLOOR_3</t>
+  </si>
+  <si>
+    <t>FLOOR_2</t>
+  </si>
+  <si>
+    <t>FLOOR_1</t>
+  </si>
+  <si>
+    <t>MTP-679</t>
+  </si>
+  <si>
+    <t>MTP-653</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -271,6 +298,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -341,7 +374,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -375,6 +408,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -691,292 +730,400 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD3C7F8-DBE7-415B-93C8-72929261549B}">
-  <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="9.765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="6" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="5" t="s">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="D10" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="D11" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="D12" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="D13" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="D14" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="D15" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
+      <c r="C18" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="D18" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="5" t="s">
+      <c r="D19" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="C20" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="D20" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="D21" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C22" s="6" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="6" t="s">
+      <c r="D22" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C23" s="8" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C20" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C21" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C22" s="5" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C23" s="5" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C24" s="5" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="10" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C25" s="5" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C26" s="10" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C27" s="11" t="s">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" s="11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C28" s="11" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>74</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C29" s="11" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="11" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C30" s="11" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C31" s="11" t="s">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>77</v>
+      </c>
+      <c r="D33" s="8" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C32" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C33" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/diag/mfg/scripts/logserver/Penang_Chamber_Config.xlsx
+++ b/diag/mfg/scripts/logserver/Penang_Chamber_Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srv1\home\winson\worksapce\psdiag\diag\mfg\scripts\logserver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B7D5E1-A836-42D0-9AD7-E727E2574EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABC1637-50ED-45FA-90FF-3DCD57F789CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="866" yWindow="-103" windowWidth="27008" windowHeight="18720" xr2:uid="{5B8EDC0A-7C03-4D41-A1A0-33B6A1F1AC78}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="81">
   <si>
     <t>Chamber 1</t>
   </si>
@@ -274,6 +274,9 @@
   </si>
   <si>
     <t>MTP-653</t>
+  </si>
+  <si>
+    <t>MTP-644</t>
   </si>
 </sst>
 </file>
@@ -420,7 +423,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{CF81C751-35C3-4D7C-834B-F1D38DCC848D}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -840,9 +851,6 @@
       </c>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
-      <c r="D8" s="5" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
@@ -850,9 +858,6 @@
       </c>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
-      <c r="D9" s="7" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
@@ -944,9 +949,6 @@
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
-      <c r="D16" s="5" t="s">
-        <v>46</v>
-      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
@@ -1062,6 +1064,9 @@
       <c r="A26" t="s">
         <v>70</v>
       </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
       <c r="D26" s="10" t="s">
         <v>61</v>
       </c>
@@ -1070,6 +1075,9 @@
       <c r="A27" t="s">
         <v>71</v>
       </c>
+      <c r="B27" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="D27" s="11" t="s">
         <v>62</v>
       </c>
@@ -1078,6 +1086,9 @@
       <c r="A28" t="s">
         <v>72</v>
       </c>
+      <c r="B28" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="D28" s="11" t="s">
         <v>63</v>
       </c>
@@ -1086,6 +1097,9 @@
       <c r="A29" t="s">
         <v>73</v>
       </c>
+      <c r="B29" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="D29" s="11" t="s">
         <v>64</v>
       </c>
@@ -1124,6 +1138,10 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="B1:D1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/diag/mfg/scripts/logserver/Penang_Chamber_Config.xlsx
+++ b/diag/mfg/scripts/logserver/Penang_Chamber_Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srv1\home\winson\worksapce\psdiag\diag\mfg\scripts\logserver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABC1637-50ED-45FA-90FF-3DCD57F789CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695D3136-96E8-4232-8685-1FF764B24431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="866" yWindow="-103" windowWidth="27008" windowHeight="18720" xr2:uid="{5B8EDC0A-7C03-4D41-A1A0-33B6A1F1AC78}"/>
+    <workbookView xWindow="883" yWindow="1020" windowWidth="12308" windowHeight="6540" xr2:uid="{5B8EDC0A-7C03-4D41-A1A0-33B6A1F1AC78}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="100">
   <si>
     <t>Chamber 1</t>
   </si>
@@ -93,9 +93,6 @@
     <t>MTP-746</t>
   </si>
   <si>
-    <t>MTP-641</t>
-  </si>
-  <si>
     <t>MTP-616</t>
   </si>
   <si>
@@ -150,9 +147,6 @@
     <t>MTP-649</t>
   </si>
   <si>
-    <t>MTP-707</t>
-  </si>
-  <si>
     <t>MTP-747</t>
   </si>
   <si>
@@ -177,9 +171,6 @@
     <t>MTP-652</t>
   </si>
   <si>
-    <t>MTP-711</t>
-  </si>
-  <si>
     <t>MTP-750</t>
   </si>
   <si>
@@ -189,36 +180,12 @@
     <t>MTP-754</t>
   </si>
   <si>
-    <t>MTP-502</t>
-  </si>
-  <si>
     <t>MTP-713</t>
   </si>
   <si>
     <t>MTP-752</t>
   </si>
   <si>
-    <t>MTP-503</t>
-  </si>
-  <si>
-    <t>MTP-504</t>
-  </si>
-  <si>
-    <t>MTP-505</t>
-  </si>
-  <si>
-    <t>MTP-506</t>
-  </si>
-  <si>
-    <t>MTP-507</t>
-  </si>
-  <si>
-    <t>MTP-508</t>
-  </si>
-  <si>
-    <t>MTP-509</t>
-  </si>
-  <si>
     <t>MTP-672</t>
   </si>
   <si>
@@ -231,12 +198,6 @@
     <t>MTP-674</t>
   </si>
   <si>
-    <t>MTP-678</t>
-  </si>
-  <si>
-    <t>MTP-677</t>
-  </si>
-  <si>
     <t>MTP-749</t>
   </si>
   <si>
@@ -270,20 +231,116 @@
     <t>FLOOR_1</t>
   </si>
   <si>
-    <t>MTP-679</t>
-  </si>
-  <si>
-    <t>MTP-653</t>
-  </si>
-  <si>
     <t>MTP-644</t>
+  </si>
+  <si>
+    <t>Chamber 4</t>
+  </si>
+  <si>
+    <t>MTP-768</t>
+  </si>
+  <si>
+    <t>MTP-771</t>
+  </si>
+  <si>
+    <t>MTP-770</t>
+  </si>
+  <si>
+    <t>MTP-767</t>
+  </si>
+  <si>
+    <t>MTP-766</t>
+  </si>
+  <si>
+    <t>MTP-760</t>
+  </si>
+  <si>
+    <t>MTP-759</t>
+  </si>
+  <si>
+    <t>MTP-717</t>
+  </si>
+  <si>
+    <t>MTP-612</t>
+  </si>
+  <si>
+    <t>MTP-765</t>
+  </si>
+  <si>
+    <t>MTP-761</t>
+  </si>
+  <si>
+    <t>MTP-683</t>
+  </si>
+  <si>
+    <t>MTP-668</t>
+  </si>
+  <si>
+    <t>MTP-667</t>
+  </si>
+  <si>
+    <t>MTP-600</t>
+  </si>
+  <si>
+    <t>MTP-613</t>
+  </si>
+  <si>
+    <t>MTP-811</t>
+  </si>
+  <si>
+    <t>MTP-763</t>
+  </si>
+  <si>
+    <t>MTP-762</t>
+  </si>
+  <si>
+    <t>MTP-769</t>
+  </si>
+  <si>
+    <t>MTP-764</t>
+  </si>
+  <si>
+    <t>MTP-735</t>
+  </si>
+  <si>
+    <t>MTP-732</t>
+  </si>
+  <si>
+    <t>MTP-736</t>
+  </si>
+  <si>
+    <t>MTP-739</t>
+  </si>
+  <si>
+    <t>MTP-756</t>
+  </si>
+  <si>
+    <t>MTP-726</t>
+  </si>
+  <si>
+    <t>MTP-733</t>
+  </si>
+  <si>
+    <t>MTP-737</t>
+  </si>
+  <si>
+    <t>MTP-757</t>
+  </si>
+  <si>
+    <t>MTP-611</t>
+  </si>
+  <si>
+    <t>MTP-738</t>
+  </si>
+  <si>
+    <t>MTP-734</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,18 +355,39 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -334,8 +412,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -372,50 +456,82 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -423,7 +539,21 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{CF81C751-35C3-4D7C-834B-F1D38DCC848D}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -741,405 +871,497 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD3C7F8-DBE7-415B-93C8-72929261549B}">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="4" width="9.765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.765625" customWidth="1"/>
+    <col min="5" max="5" width="9.765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="D4" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="D5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
+      <c r="D6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="D7" s="5"/>
+      <c r="E7" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+      <c r="C10" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="D10" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>72</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="5" t="s">
+      <c r="D18" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="5" t="s">
+    <row r="19" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="5" t="s">
+    <row r="20" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>70</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>72</v>
-      </c>
-      <c r="B20" s="5" t="s">
+    <row r="21" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E25" s="12"/>
+    </row>
+    <row r="26" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A26" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" s="13"/>
+      <c r="E26" s="14"/>
+    </row>
+    <row r="27" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A27" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" s="13"/>
+      <c r="E27" s="15"/>
+    </row>
+    <row r="28" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A28" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
-        <v>75</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>77</v>
-      </c>
-      <c r="D25" s="5" t="s">
+      <c r="C28" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28" s="13"/>
+      <c r="E28" s="15"/>
+    </row>
+    <row r="29" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A29" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
-        <v>70</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="10" t="s">
+      <c r="B29" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" s="13"/>
+      <c r="E29" s="15"/>
+    </row>
+    <row r="30" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A30" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" s="11" t="s">
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="15"/>
+    </row>
+    <row r="31" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>72</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D28" s="11" t="s">
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="15"/>
+    </row>
+    <row r="32" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A32" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
-        <v>73</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D29" s="11" t="s">
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="16"/>
+    </row>
+    <row r="33" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
-        <v>74</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
-        <v>75</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A32" t="s">
-        <v>76</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A33" t="s">
-        <v>77</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>68</v>
-      </c>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="17"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="B1:D1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="B1:E1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/diag/mfg/scripts/logserver/Penang_Chamber_Config.xlsx
+++ b/diag/mfg/scripts/logserver/Penang_Chamber_Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srv1\home\winson\worksapce\psdiag\diag\mfg\scripts\logserver\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/home/winson/worksapce/psdiag/diag/mfg/scripts/logserver/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695D3136-96E8-4232-8685-1FF764B24431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{753A12C4-1299-0E44-9937-58C7CCDA4DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="883" yWindow="1020" windowWidth="12308" windowHeight="6540" xr2:uid="{5B8EDC0A-7C03-4D41-A1A0-33B6A1F1AC78}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="30720" windowHeight="17480" xr2:uid="{5B8EDC0A-7C03-4D41-A1A0-33B6A1F1AC78}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="102">
   <si>
     <t>Chamber 1</t>
   </si>
@@ -51,18 +51,12 @@
     <t>MTP-741</t>
   </si>
   <si>
-    <t>MTP-601</t>
-  </si>
-  <si>
     <t>MTP-632</t>
   </si>
   <si>
     <t>MTP-742</t>
   </si>
   <si>
-    <t>MTP-602</t>
-  </si>
-  <si>
     <t>MTP-633</t>
   </si>
   <si>
@@ -75,9 +69,6 @@
     <t>MTP-634</t>
   </si>
   <si>
-    <t>MTP-615</t>
-  </si>
-  <si>
     <t>MTP-662</t>
   </si>
   <si>
@@ -93,75 +84,33 @@
     <t>MTP-746</t>
   </si>
   <si>
-    <t>MTP-616</t>
-  </si>
-  <si>
     <t>MTP-637</t>
   </si>
   <si>
     <t>MTP-642</t>
   </si>
   <si>
-    <t>MTP-617</t>
-  </si>
-  <si>
-    <t>MTP-623</t>
-  </si>
-  <si>
     <t>MTP-643</t>
   </si>
   <si>
-    <t>MTP-618</t>
-  </si>
-  <si>
     <t>MTP-656</t>
   </si>
   <si>
-    <t>MTP-646</t>
-  </si>
-  <si>
-    <t>MTP-619</t>
-  </si>
-  <si>
-    <t>MTP-710</t>
-  </si>
-  <si>
     <t>MTP-647</t>
   </si>
   <si>
-    <t>MTP-620</t>
-  </si>
-  <si>
-    <t>MTP-714</t>
-  </si>
-  <si>
     <t>MTP-648</t>
   </si>
   <si>
-    <t>MTP-621</t>
-  </si>
-  <si>
-    <t>MTP-636</t>
-  </si>
-  <si>
-    <t>MTP-649</t>
-  </si>
-  <si>
     <t>MTP-747</t>
   </si>
   <si>
-    <t>MTP-650</t>
-  </si>
-  <si>
     <t>MTP-708</t>
   </si>
   <si>
     <t>MTP-748</t>
   </si>
   <si>
-    <t>MTP-651</t>
-  </si>
-  <si>
     <t>MTP-709</t>
   </si>
   <si>
@@ -198,9 +147,6 @@
     <t>MTP-674</t>
   </si>
   <si>
-    <t>MTP-749</t>
-  </si>
-  <si>
     <t>MTP-751</t>
   </si>
   <si>
@@ -237,12 +183,6 @@
     <t>Chamber 4</t>
   </si>
   <si>
-    <t>MTP-768</t>
-  </si>
-  <si>
-    <t>MTP-771</t>
-  </si>
-  <si>
     <t>MTP-770</t>
   </si>
   <si>
@@ -255,39 +195,12 @@
     <t>MTP-760</t>
   </si>
   <si>
-    <t>MTP-759</t>
-  </si>
-  <si>
     <t>MTP-717</t>
   </si>
   <si>
-    <t>MTP-612</t>
-  </si>
-  <si>
-    <t>MTP-765</t>
-  </si>
-  <si>
     <t>MTP-761</t>
   </si>
   <si>
-    <t>MTP-683</t>
-  </si>
-  <si>
-    <t>MTP-668</t>
-  </si>
-  <si>
-    <t>MTP-667</t>
-  </si>
-  <si>
-    <t>MTP-600</t>
-  </si>
-  <si>
-    <t>MTP-613</t>
-  </si>
-  <si>
-    <t>MTP-811</t>
-  </si>
-  <si>
     <t>MTP-763</t>
   </si>
   <si>
@@ -309,9 +222,6 @@
     <t>MTP-736</t>
   </si>
   <si>
-    <t>MTP-739</t>
-  </si>
-  <si>
     <t>MTP-756</t>
   </si>
   <si>
@@ -334,13 +244,109 @@
   </si>
   <si>
     <t>MTP-734</t>
+  </si>
+  <si>
+    <t>MTP-794</t>
+  </si>
+  <si>
+    <t>MTP-795</t>
+  </si>
+  <si>
+    <t>MTP-796</t>
+  </si>
+  <si>
+    <t>MTP-797</t>
+  </si>
+  <si>
+    <t>MTP-798</t>
+  </si>
+  <si>
+    <t>MTP-815</t>
+  </si>
+  <si>
+    <t>MTP-799</t>
+  </si>
+  <si>
+    <t>MTP-675</t>
+  </si>
+  <si>
+    <t>MTP-678</t>
+  </si>
+  <si>
+    <t>MTP-629</t>
+  </si>
+  <si>
+    <t>MTP-730</t>
+  </si>
+  <si>
+    <t>MTP-704</t>
+  </si>
+  <si>
+    <t>MTP-778</t>
+  </si>
+  <si>
+    <t>MTP-780</t>
+  </si>
+  <si>
+    <t>MTP-779</t>
+  </si>
+  <si>
+    <t>MTP-777</t>
+  </si>
+  <si>
+    <t>MTP-676</t>
+  </si>
+  <si>
+    <t>MTP-814</t>
+  </si>
+  <si>
+    <t>MTP-775</t>
+  </si>
+  <si>
+    <t>MTP-776</t>
+  </si>
+  <si>
+    <t>MTP-793</t>
+  </si>
+  <si>
+    <t>MTP-789</t>
+  </si>
+  <si>
+    <t>MTP-790</t>
+  </si>
+  <si>
+    <t>MTP-791</t>
+  </si>
+  <si>
+    <t>MTP-786</t>
+  </si>
+  <si>
+    <t>MTP-809</t>
+  </si>
+  <si>
+    <t>MTP-812</t>
+  </si>
+  <si>
+    <t>MTP-785</t>
+  </si>
+  <si>
+    <t>MTP-787</t>
+  </si>
+  <si>
+    <t>MTP-788</t>
+  </si>
+  <si>
+    <t>MTP-782</t>
+  </si>
+  <si>
+    <t>Chamber 5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -386,8 +392,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -402,24 +414,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="26"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -431,15 +431,6 @@
       <left style="thin">
         <color indexed="8"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="thin">
         <color indexed="8"/>
@@ -473,10 +464,10 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="hair">
-        <color indexed="8"/>
-      </top>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -485,7 +476,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -494,10 +485,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -507,53 +498,40 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{CF81C751-35C3-4D7C-834B-F1D38DCC848D}"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
@@ -871,17 +849,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD3C7F8-DBE7-415B-93C8-72929261549B}">
-  <dimension ref="A1:E33"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="3" width="9.765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.765625" customWidth="1"/>
-    <col min="5" max="5" width="9.765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.83203125" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -893,475 +871,519 @@
         <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="15" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A5" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A7" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="F7" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="8"/>
     </row>
-    <row r="10" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="4" t="s">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A11" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A12" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A13" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A14" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A15" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A16" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A17" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A18" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A19" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A20" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A21" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E21" s="4" t="s">
+      <c r="E23" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A22" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A23" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A24" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
-      <c r="D24" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="D24" s="10"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="10"/>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="12"/>
-    </row>
-    <row r="26" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A26" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" s="13"/>
-      <c r="E26" s="14"/>
-    </row>
-    <row r="27" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A27" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D27" s="13"/>
-      <c r="E27" s="15"/>
-    </row>
-    <row r="28" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A28" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" s="4" t="s">
+      <c r="D29" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="15"/>
-    </row>
-    <row r="29" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A29" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="15"/>
-    </row>
-    <row r="30" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A30" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="15"/>
-    </row>
-    <row r="31" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A31" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="8"/>
+      <c r="B31" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="15"/>
-    </row>
-    <row r="32" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="D31" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="16"/>
+    </row>
+    <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
-      <c r="E32" s="16"/>
-    </row>
-    <row r="33" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="17"/>
     </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E34" s="18"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="B1:E1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  <conditionalFormatting sqref="B1:E1048576 F1:F7 F10:F15">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
